--- a/resultado_urls2.xlsx
+++ b/resultado_urls2.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D248"/>
+  <dimension ref="A1:D129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>❌ NO ENCONTRADA (404)</t>
+          <t>❌ SIN CONEXIÓN</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>❌ NO ENCONTRADA (404)</t>
+          <t>❌ SIN CONEXIÓN</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>❌ NO ENCONTRADA (404)</t>
+          <t>❌ SIN CONEXIÓN</t>
         </is>
       </c>
     </row>
@@ -2773,17 +2773,17 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/tercera-dimension</t>
+          <t>https://ash.buenosaires.gob.ar/copidis/publicaciones/guia-de-turismo-accesible-201819-0</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/tercera-dimension</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
+          <t>https://ash.buenosaires.gob.ar/copidis/publicaciones/guia-de-turismo-accesible-201819-0</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>❌ SIN CONEXIÓN</t>
         </is>
       </c>
     </row>
@@ -2793,17 +2793,17 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/primeras-flores-taller-de-haiku-en-el-jardin</t>
+          <t>https://buenosaires.gob.ar/transito</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/primeras-flores-taller-de-haiku-en-el-jardin</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
+          <t>https://buenosaires.gob.ar/transito</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>✅ ONLINE (HTTP 200)</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/habitamos-la-memoria-de-gardel</t>
+          <t>https://mapa.buenosaires.gob.ar/comollego/?lat=-34.640326&amp;lng=-58.407019&amp;zl=15&amp;modo=transporte&amp;dir=Uspallata+3160</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/habitamos-la-memoria-de-gardel</t>
-        </is>
-      </c>
-      <c r="D118" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
+          <t>https://mapa.buenosaires.gob.ar/comollego/?lat=-34.640326&amp;lng=-58.407019&amp;zl=15&amp;modo=transporte&amp;dir=Uspallata+3160</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>✅ ONLINE (HTTP 200)</t>
         </is>
       </c>
     </row>
@@ -2833,17 +2833,17 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/feria-de-mataderos</t>
+          <t>https://formulario-sigeci.buenosaires.gob.ar/InicioTramite?idPrestacion=7489.</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/feria-de-mataderos</t>
-        </is>
-      </c>
-      <c r="D119" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
+          <t>https://formulario-sigeci.buenosaires.gob.ar/InicioTramite?idPrestacion=7489</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>✅ ONLINE (HTTP 200)</t>
         </is>
       </c>
     </row>
@@ -2853,17 +2853,17 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/chorifest</t>
+          <t>https://static.buenosaires.gob.ar/gcaba_historico/tramites/registro-de-plano-de-propiedad-horizontal-nuevo</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/chorifest</t>
-        </is>
-      </c>
-      <c r="D120" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
+          <t>https://static.buenosaires.gob.ar/gcaba_historico/tramites/registro-de-plano-de-propiedad-horizontal-nuevo</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>✅ ONLINE (HTTP 200)</t>
         </is>
       </c>
     </row>
@@ -2873,17 +2873,17 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/feria-nuevos-sabores-parque-chacabuco</t>
+          <t>https://static.buenosaires.gob.ar/gcaba_historico/tramites/registro-de-plano-de-propiedad-horizontal-modificatorio-o-complementario</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/feria-nuevos-sabores-parque-chacabuco</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
+          <t>https://static.buenosaires.gob.ar/gcaba_historico/tramites/registro-de-plano-de-propiedad-horizontal-modificatorio-o-complementario</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>✅ ONLINE (HTTP 200)</t>
         </is>
       </c>
     </row>
@@ -2893,17 +2893,17 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/festival-vegano</t>
+          <t>https://buenosaires.gob.ar/apoyo-para-la-vida-independiente</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/festival-vegano</t>
+          <t>https://buenosaires.gob.ar/apoyo-para-la-vida-independiente</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>❌ ERROR HTTP 500</t>
+          <t>❌ NO ENCONTRADA (404)</t>
         </is>
       </c>
     </row>
@@ -2913,17 +2913,17 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/verano-en-el-parque-de-la-ciudad</t>
+          <t>https://gestioncolaborativa.buenosaires.gob.ar/prestaciones.</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/verano-en-el-parque-de-la-ciudad</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
+          <t>https://gestioncolaborativa.buenosaires.gob.ar/prestaciones</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>✅ ONLINE (HTTP 200)</t>
         </is>
       </c>
     </row>
@@ -2933,17 +2933,17 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/experiencia-ba</t>
+          <t>https://buenosaires.gob.ar/jefaturadegabinete/deportes/arranca-la-inscripcion-las-colonias-deportivas-de-verano-2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/experiencia-ba</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
+          <t>https://buenosaires.gob.ar/jefaturadegabinete/deportes/arranca-la-inscripcion-las-colonias-deportivas-de-verano-2026</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>❌ NO ENCONTRADA (404)</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/noches-de-cine</t>
+          <t>https://static.buenosaires.gob.ar/gcaba_historico/desarrollohumanoyhabitat/inclusion-social-y-atencion-inmediata/atencion-social/sedes-de-atencion</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/noches-de-cine</t>
-        </is>
-      </c>
-      <c r="D125" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
+          <t>https://static.buenosaires.gob.ar/gcaba_historico/desarrollohumanoyhabitat/inclusion-social-y-atencion-inmediata/atencion-social/sedes-de-atencion</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>✅ ONLINE (HTTP 200)</t>
         </is>
       </c>
     </row>
@@ -2973,17 +2973,17 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/yoga-en-silla</t>
+          <t>https://buenosaires.gob.ar/gcaba_historico/vicejefatura/ba-discapacidad/capacitacion-de-asistentes-personales-para-la-vida-independiente-para</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/yoga-en-silla</t>
-        </is>
-      </c>
-      <c r="D126" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
+          <t>https://buenosaires.gob.ar/gcaba_historico/vicejefatura/ba-discapacidad/capacitacion-de-asistentes-personales-para-la-vida-independiente-para</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>✅ ONLINE (HTTP 200)</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/conciertos-al-mediodia-orquesta-del-tango-de-buenos-aires</t>
+          <t>http://static.buenosaires.gob.ar/gcaba_historico/banco-de-elementos-ortopedicos-beo</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/conciertos-al-mediodia-orquesta-del-tango-de-buenos-aires</t>
-        </is>
-      </c>
-      <c r="D127" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
+          <t>http://static.buenosaires.gob.ar/gcaba_historico/banco-de-elementos-ortopedicos-beo</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>✅ ONLINE (HTTP 200)</t>
         </is>
       </c>
     </row>
@@ -3013,17 +3013,17 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/historias-de-tango</t>
+          <t>https://www.buenosaires.gob.ar/copidis</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/historias-de-tango</t>
+          <t>https://www.buenosaires.gob.ar/copidis</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>❌ ERROR HTTP 500</t>
+          <t>❌ NO ENCONTRADA (404)</t>
         </is>
       </c>
     </row>
@@ -3033,2397 +3033,17 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/sabe-la-tierra-plaza-emilio-mitre</t>
+          <t>https://www.rals.org.ar/</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>https://buenosaires.gob.ar/descubrir/sabe-la-tierra-plaza-emilio-mitre</t>
+          <t>https://www.rals.org.ar/</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
           <t>✅ ONLINE (HTTP 200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/colon-para-ninos-el-lago-de-los-cisnes</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/colon-para-ninos-el-lago-de-los-cisnes</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
-        <v>130</v>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/lineas-magicas-arte-en-relieve</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/lineas-magicas-arte-en-relieve</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/recorrido-accesible-en-lenguaje-claro</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/recorrido-accesible-en-lenguaje-claro</t>
-        </is>
-      </c>
-      <c r="D132" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/catedral-san-gregorio-el-iluminador</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/catedral-san-gregorio-el-iluminador</t>
-        </is>
-      </c>
-      <c r="D133" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/ba-market-parque-centenario</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/ba-market-parque-centenario</t>
-        </is>
-      </c>
-      <c r="D134" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/banda-sinfonica-de-la-ciudad-de-buenos-aires</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/banda-sinfonica-de-la-ciudad-de-buenos-aires</t>
-        </is>
-      </c>
-      <c r="D135" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/feria-migrante-parque-centenario</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/feria-migrante-parque-centenario</t>
-        </is>
-      </c>
-      <c r="D136" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>136</v>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/congreso-de-la-nacion</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/congreso-de-la-nacion</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="n">
-        <v>137</v>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/orquesta-filarmonica-de-buenos-aires</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/orquesta-filarmonica-de-buenos-aires</t>
-        </is>
-      </c>
-      <c r="D138" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/duo-de-flautas-patricia-da-dalt-y-beatriz-plana</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/duo-de-flautas-patricia-da-dalt-y-beatriz-plana</t>
-        </is>
-      </c>
-      <c r="D139" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/plaza-del-congreso</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/plaza-del-congreso</t>
-        </is>
-      </c>
-      <c r="D140" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/las-tres-ecologias-radioterrena-auralidades-del-rio</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/las-tres-ecologias-radioterrena-auralidades-del-rio</t>
-        </is>
-      </c>
-      <c r="D141" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="n">
-        <v>141</v>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/carlita-en-el-puente-de-la-mujer</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/carlita-en-el-puente-de-la-mujer</t>
-        </is>
-      </c>
-      <c r="D142" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="n">
-        <v>142</v>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/avenida-corrientes</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/avenida-corrientes</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="n">
-        <v>143</v>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/un-cafe-con-aroma-libertad</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/un-cafe-con-aroma-libertad</t>
-        </is>
-      </c>
-      <c r="D144" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="n">
-        <v>144</v>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/entre-el-sonido-y-el-tiempo</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/entre-el-sonido-y-el-tiempo</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="n">
-        <v>145</v>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/sabores-del-mundo-peru-mercado-san-nicolas</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/sabores-del-mundo-peru-mercado-san-nicolas</t>
-        </is>
-      </c>
-      <c r="D146" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="n">
-        <v>146</v>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/sabores-del-mundo-espana-mercado-belgrano</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/sabores-del-mundo-espana-mercado-belgrano</t>
-        </is>
-      </c>
-      <c r="D147" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/feria-francesa</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/feria-francesa</t>
-        </is>
-      </c>
-      <c r="D148" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/artlab-en-vivo-presenta-ekathe-live</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/artlab-en-vivo-presenta-ekathe-live</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="n">
-        <v>149</v>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/musica-en-el-balcon</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/musica-en-el-balcon</t>
-        </is>
-      </c>
-      <c r="D150" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/barrio-de-belgrano</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/barrio-de-belgrano</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="n">
-        <v>151</v>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/buenos-aires-cuatro-momentos-de-su-historia</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/buenos-aires-cuatro-momentos-de-su-historia</t>
-        </is>
-      </c>
-      <c r="D152" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="n">
-        <v>152</v>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/automovil-club-argentino-miradores-de-la-ciudad</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/automovil-club-argentino-miradores-de-la-ciudad</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="n">
-        <v>153</v>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/fundacion-cassara-miradores-de-la-ciudad</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/fundacion-cassara-miradores-de-la-ciudad</t>
-        </is>
-      </c>
-      <c r="D154" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="n">
-        <v>154</v>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/convivencia-en-movimiento</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/convivencia-en-movimiento</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="n">
-        <v>155</v>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/cazadores-de-sonidos</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/cazadores-de-sonidos</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="n">
-        <v>156</v>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/taller-de-pintura-naturaleza-neon</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/taller-de-pintura-naturaleza-neon</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>https://ash.buenosaires.gob.ar/copidis/publicaciones/guia-de-turismo-accesible-201819-0</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>https://ash.buenosaires.gob.ar/copidis/publicaciones/guia-de-turismo-accesible-201819-0</t>
-        </is>
-      </c>
-      <c r="D158" s="4" t="inlineStr">
-        <is>
-          <t>❌ NO ENCONTRADA (404)</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="n">
-        <v>158</v>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/feria-nuevos-sabores-parque-rivadavia</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/feria-nuevos-sabores-parque-rivadavia</t>
-        </is>
-      </c>
-      <c r="D159" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/plaza-de-mayo</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/plaza-de-mayo</t>
-        </is>
-      </c>
-      <c r="D160" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="n">
-        <v>160</v>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/parque-rivadavia</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/parque-rivadavia</t>
-        </is>
-      </c>
-      <c r="D161" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="n">
-        <v>161</v>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/parque-lezama</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/parque-lezama</t>
-        </is>
-      </c>
-      <c r="D162" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="n">
-        <v>162</v>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/basilica-santa-rosa-de-lima-miradores-de-la-ciudad</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/basilica-santa-rosa-de-lima-miradores-de-la-ciudad</t>
-        </is>
-      </c>
-      <c r="D163" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="n">
-        <v>163</v>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/experiencia-gastronomica-en-el-mercado-de-san-nicolas</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/experiencia-gastronomica-en-el-mercado-de-san-nicolas</t>
-        </is>
-      </c>
-      <c r="D164" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="n">
-        <v>164</v>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/la-ultima-fortaleza</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/la-ultima-fortaleza</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="n">
-        <v>165</v>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/seminario-rabinico-latinoamericano</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/seminario-rabinico-latinoamericano</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="n">
-        <v>166</v>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/luz-gaggi-deslumbro-en-calle-corrientes</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/luz-gaggi-deslumbro-en-calle-corrientes</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="n">
-        <v>167</v>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/galeria-guemes-miradores-de-la-ciudad</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/galeria-guemes-miradores-de-la-ciudad</t>
-        </is>
-      </c>
-      <c r="D168" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="n">
-        <v>168</v>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/edificio-miguel-bencich-miradores-de-la-ciudad</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/edificio-miguel-bencich-miradores-de-la-ciudad</t>
-        </is>
-      </c>
-      <c r="D169" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="n">
-        <v>169</v>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/plaza-mitre-miradores-de-la-ciudad</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/plaza-mitre-miradores-de-la-ciudad</t>
-        </is>
-      </c>
-      <c r="D170" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="n">
-        <v>170</v>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/agujeros-negros-supermasivos</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/agujeros-negros-supermasivos</t>
-        </is>
-      </c>
-      <c r="D171" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="n">
-        <v>171</v>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/la-primera-cancha-de-futbol-argentino</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/la-primera-cancha-de-futbol-argentino</t>
-        </is>
-      </c>
-      <c r="D172" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="n">
-        <v>172</v>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/inauguracion-el-azulejo-en-el-rio-de-la-plata-1949-2026</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/inauguracion-el-azulejo-en-el-rio-de-la-plata-1949-2026</t>
-        </is>
-      </c>
-      <c r="D173" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="n">
-        <v>173</v>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/juguemos-bajo-el-ombu</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/juguemos-bajo-el-ombu</t>
-        </is>
-      </c>
-      <c r="D174" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="n">
-        <v>174</v>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/cine-bajo-las-estrellas</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/cine-bajo-las-estrellas</t>
-        </is>
-      </c>
-      <c r="D175" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="n">
-        <v>175</v>
-      </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/feria-nuevos-sabores-plazoleta-guemes</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/feria-nuevos-sabores-plazoleta-guemes</t>
-        </is>
-      </c>
-      <c r="D176" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="n">
-        <v>176</v>
-      </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/ba-market-plaza-zapiola</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/ba-market-plaza-zapiola</t>
-        </is>
-      </c>
-      <c r="D177" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="n">
-        <v>177</v>
-      </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/ba-flota</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/ba-flota</t>
-        </is>
-      </c>
-      <c r="D178" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="n">
-        <v>178</v>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/paseo-ambiental-del-sur</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/paseo-ambiental-del-sur</t>
-        </is>
-      </c>
-      <c r="D179" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="n">
-        <v>179</v>
-      </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/milonga-del-cc25</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/milonga-del-cc25</t>
-        </is>
-      </c>
-      <c r="D180" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/literatura-en-el-parque-lezama-recorrido-tematico</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/literatura-en-el-parque-lezama-recorrido-tematico</t>
-        </is>
-      </c>
-      <c r="D181" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="n">
-        <v>181</v>
-      </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/trama-edicion-especial</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/trama-edicion-especial</t>
-        </is>
-      </c>
-      <c r="D182" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="n">
-        <v>182</v>
-      </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/caleidoscopio</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/caleidoscopio</t>
-        </is>
-      </c>
-      <c r="D183" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/ludo-espacio</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/ludo-espacio</t>
-        </is>
-      </c>
-      <c r="D184" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="n">
-        <v>184</v>
-      </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/taller-retratos-que-hablan</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/taller-retratos-que-hablan</t>
-        </is>
-      </c>
-      <c r="D185" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="n">
-        <v>185</v>
-      </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/baco-polaco</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/baco-polaco</t>
-        </is>
-      </c>
-      <c r="D186" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="n">
-        <v>186</v>
-      </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/temporada-de-conciertos-2026-salon-dorado-del-teatro-colon</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/temporada-de-conciertos-2026-salon-dorado-del-teatro-colon</t>
-        </is>
-      </c>
-      <c r="D187" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="n">
-        <v>187</v>
-      </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/historias-secretas-del-teatro-colon</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/historias-secretas-del-teatro-colon</t>
-        </is>
-      </c>
-      <c r="D188" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="n">
-        <v>188</v>
-      </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/mi-contundente-situacion</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/mi-contundente-situacion</t>
-        </is>
-      </c>
-      <c r="D189" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="n">
-        <v>189</v>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/dia-mundial-del-arte-museo-larreta</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/dia-mundial-del-arte-museo-larreta</t>
-        </is>
-      </c>
-      <c r="D190" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="n">
-        <v>190</v>
-      </c>
-      <c r="B191" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/monte-castro-ciclo-de-charlas</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/monte-castro-ciclo-de-charlas</t>
-        </is>
-      </c>
-      <c r="D191" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="n">
-        <v>191</v>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/daisy-lombardo-y-ramiro-gallo-quinteto</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/daisy-lombardo-y-ramiro-gallo-quinteto</t>
-        </is>
-      </c>
-      <c r="D192" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="n">
-        <v>192</v>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/las-pastillas-del-abuelo</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/las-pastillas-del-abuelo</t>
-        </is>
-      </c>
-      <c r="D193" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="n">
-        <v>193</v>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/antonio-tarrago-ros</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/antonio-tarrago-ros</t>
-        </is>
-      </c>
-      <c r="D194" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="n">
-        <v>194</v>
-      </c>
-      <c r="B195" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/sunsetstrip-buenos-aires</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/sunsetstrip-buenos-aires</t>
-        </is>
-      </c>
-      <c r="D195" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="n">
-        <v>195</v>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/pena-en-la-casa-de-la-cultura</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/pena-en-la-casa-de-la-cultura</t>
-        </is>
-      </c>
-      <c r="D196" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="n">
-        <v>196</v>
-      </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/tertulias-liricas</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/tertulias-liricas</t>
-        </is>
-      </c>
-      <c r="D197" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="n">
-        <v>197</v>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/ateneo-para-una-familia</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/ateneo-para-una-familia</t>
-        </is>
-      </c>
-      <c r="D198" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/laila-speciale-quartet</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/laila-speciale-quartet</t>
-        </is>
-      </c>
-      <c r="D199" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="n">
-        <v>199</v>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/cuarteto-en-concierto</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/cuarteto-en-concierto</t>
-        </is>
-      </c>
-      <c r="D200" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/jazz-buenos-aires</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/jazz-buenos-aires</t>
-        </is>
-      </c>
-      <c r="D201" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="n">
-        <v>201</v>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/torre-monumental-miradores-de-la-ciudad</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/torre-monumental-miradores-de-la-ciudad</t>
-        </is>
-      </c>
-      <c r="D202" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="n">
-        <v>202</v>
-      </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/caminos-y-sabores</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/caminos-y-sabores</t>
-        </is>
-      </c>
-      <c r="D203" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="n">
-        <v>203</v>
-      </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/palacio-libertad</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/palacio-libertad</t>
-        </is>
-      </c>
-      <c r="D204" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="n">
-        <v>204</v>
-      </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/cine-en-el-casco-historico</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/cine-en-el-casco-historico</t>
-        </is>
-      </c>
-      <c r="D205" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/sabe-la-tierra-devoto</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/sabe-la-tierra-devoto</t>
-        </is>
-      </c>
-      <c r="D206" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="2" t="n">
-        <v>206</v>
-      </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/en-voz-alta</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/en-voz-alta</t>
-        </is>
-      </c>
-      <c r="D207" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="n">
-        <v>207</v>
-      </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/jornada-de-adopcion</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/jornada-de-adopcion</t>
-        </is>
-      </c>
-      <c r="D208" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="n">
-        <v>208</v>
-      </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/guerreras-doradas</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/guerreras-doradas</t>
-        </is>
-      </c>
-      <c r="D209" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="n">
-        <v>209</v>
-      </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/concierto-entre-almohadones-el-carnaval-de-los-animales-y-otras-musicas</t>
-        </is>
-      </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/concierto-entre-almohadones-el-carnaval-de-los-animales-y-otras-musicas</t>
-        </is>
-      </c>
-      <c r="D210" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="n">
-        <v>210</v>
-      </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/lumiere-quinteto</t>
-        </is>
-      </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/lumiere-quinteto</t>
-        </is>
-      </c>
-      <c r="D211" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="n">
-        <v>211</v>
-      </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/veo-veo</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/veo-veo</t>
-        </is>
-      </c>
-      <c r="D212" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="n">
-        <v>212</v>
-      </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/travesia-intergalactica</t>
-        </is>
-      </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/travesia-intergalactica</t>
-        </is>
-      </c>
-      <c r="D213" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="n">
-        <v>213</v>
-      </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/presentacion-del-libro-los-tiempos-de-la-colonia</t>
-        </is>
-      </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/presentacion-del-libro-los-tiempos-de-la-colonia</t>
-        </is>
-      </c>
-      <c r="D214" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="n">
-        <v>214</v>
-      </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/50deg-feria-internacional-del-libro-de-buenos-aires</t>
-        </is>
-      </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/50deg-feria-internacional-del-libro-de-buenos-aires</t>
-        </is>
-      </c>
-      <c r="D215" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="n">
-        <v>215</v>
-      </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/visita-al-reloj-de-la-torre-monumental</t>
-        </is>
-      </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/visita-al-reloj-de-la-torre-monumental</t>
-        </is>
-      </c>
-      <c r="D216" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="n">
-        <v>216</v>
-      </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/casal-de-catalunya</t>
-        </is>
-      </c>
-      <c r="C217" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/casal-de-catalunya</t>
-        </is>
-      </c>
-      <c r="D217" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="n">
-        <v>217</v>
-      </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/taller-actuar-y-escribir</t>
-        </is>
-      </c>
-      <c r="C218" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/taller-actuar-y-escribir</t>
-        </is>
-      </c>
-      <c r="D218" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="n">
-        <v>218</v>
-      </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/cine-bajo-las-estrellas-0</t>
-        </is>
-      </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/cine-bajo-las-estrellas-0</t>
-        </is>
-      </c>
-      <c r="D219" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="n">
-        <v>219</v>
-      </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/ba-celebra-america</t>
-        </is>
-      </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/ba-celebra-america</t>
-        </is>
-      </c>
-      <c r="D220" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="n">
-        <v>220</v>
-      </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/trama</t>
-        </is>
-      </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/trama</t>
-        </is>
-      </c>
-      <c r="D221" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="n">
-        <v>221</v>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/historias-de-tango-1</t>
-        </is>
-      </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/historias-de-tango-1</t>
-        </is>
-      </c>
-      <c r="D222" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="n">
-        <v>222</v>
-      </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/70deg-aniversario-del-museo-moderno</t>
-        </is>
-      </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/70deg-aniversario-del-museo-moderno</t>
-        </is>
-      </c>
-      <c r="D223" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="n">
-        <v>223</v>
-      </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/fulgor</t>
-        </is>
-      </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/fulgor</t>
-        </is>
-      </c>
-      <c r="D224" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="n">
-        <v>224</v>
-      </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/red-de-escucha-y-acompanamiento</t>
-        </is>
-      </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/red-de-escucha-y-acompanamiento</t>
-        </is>
-      </c>
-      <c r="D225" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="n">
-        <v>225</v>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/campeonato-federal-de-ahumados</t>
-        </is>
-      </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/campeonato-federal-de-ahumados</t>
-        </is>
-      </c>
-      <c r="D226" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="n">
-        <v>226</v>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/mirador-edificio-massimiliano-bencich</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/mirador-edificio-massimiliano-bencich</t>
-        </is>
-      </c>
-      <c r="D227" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="n">
-        <v>227</v>
-      </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/bioferia</t>
-        </is>
-      </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/bioferia</t>
-        </is>
-      </c>
-      <c r="D228" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="n">
-        <v>228</v>
-      </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/museo-historico-de-salud-mental-del-hospital-jose-t-borda</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/museo-historico-de-salud-mental-del-hospital-jose-t-borda</t>
-        </is>
-      </c>
-      <c r="D229" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="n">
-        <v>229</v>
-      </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/rio-bravo</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/rio-bravo</t>
-        </is>
-      </c>
-      <c r="D230" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="n">
-        <v>230</v>
-      </c>
-      <c r="B231" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/transito</t>
-        </is>
-      </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/transito</t>
-        </is>
-      </c>
-      <c r="D231" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="n">
-        <v>231</v>
-      </c>
-      <c r="B232" s="2" t="inlineStr">
-        <is>
-          <t>https://mapa.buenosaires.gob.ar/comollego/?lat=-34.640326&amp;lng=-58.407019&amp;zl=15&amp;modo=transporte&amp;dir=Uspallata+3160</t>
-        </is>
-      </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>https://mapa.buenosaires.gob.ar/comollego/?lat=-34.640326&amp;lng=-58.407019&amp;zl=15&amp;modo=transporte&amp;dir=Uspallata+3160</t>
-        </is>
-      </c>
-      <c r="D232" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="2" t="n">
-        <v>232</v>
-      </c>
-      <c r="B233" s="2" t="inlineStr">
-        <is>
-          <t>https://formulario-sigeci.buenosaires.gob.ar/InicioTramite?idPrestacion=7489.</t>
-        </is>
-      </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>https://formulario-sigeci.buenosaires.gob.ar/InicioTramite?idPrestacion=7489</t>
-        </is>
-      </c>
-      <c r="D233" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="n">
-        <v>233</v>
-      </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>https://static.buenosaires.gob.ar/gcaba_historico/tramites/registro-de-plano-de-propiedad-horizontal-nuevo</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>https://static.buenosaires.gob.ar/gcaba_historico/tramites/registro-de-plano-de-propiedad-horizontal-nuevo</t>
-        </is>
-      </c>
-      <c r="D234" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="n">
-        <v>234</v>
-      </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>https://static.buenosaires.gob.ar/gcaba_historico/tramites/registro-de-plano-de-propiedad-horizontal-modificatorio-o-complementario</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>https://static.buenosaires.gob.ar/gcaba_historico/tramites/registro-de-plano-de-propiedad-horizontal-modificatorio-o-complementario</t>
-        </is>
-      </c>
-      <c r="D235" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="n">
-        <v>235</v>
-      </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/apoyo-para-la-vida-independiente</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/apoyo-para-la-vida-independiente</t>
-        </is>
-      </c>
-      <c r="D236" s="4" t="inlineStr">
-        <is>
-          <t>❌ NO ENCONTRADA (404)</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="n">
-        <v>236</v>
-      </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>https://gestioncolaborativa.buenosaires.gob.ar/prestaciones.</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>https://gestioncolaborativa.buenosaires.gob.ar/prestaciones</t>
-        </is>
-      </c>
-      <c r="D237" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="n">
-        <v>237</v>
-      </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/jefaturadegabinete/deportes/arranca-la-inscripcion-las-colonias-deportivas-de-verano-2026</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/jefaturadegabinete/deportes/arranca-la-inscripcion-las-colonias-deportivas-de-verano-2026</t>
-        </is>
-      </c>
-      <c r="D238" s="4" t="inlineStr">
-        <is>
-          <t>❌ NO ENCONTRADA (404)</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="n">
-        <v>238</v>
-      </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>https://static.buenosaires.gob.ar/gcaba_historico/desarrollohumanoyhabitat/inclusion-social-y-atencion-inmediata/atencion-social/sedes-de-atencion</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>https://static.buenosaires.gob.ar/gcaba_historico/desarrollohumanoyhabitat/inclusion-social-y-atencion-inmediata/atencion-social/sedes-de-atencion</t>
-        </is>
-      </c>
-      <c r="D239" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="n">
-        <v>239</v>
-      </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/gcaba_historico/vicejefatura/ba-discapacidad/capacitacion-de-asistentes-personales-para-la-vida-independiente-para</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/gcaba_historico/vicejefatura/ba-discapacidad/capacitacion-de-asistentes-personales-para-la-vida-independiente-para</t>
-        </is>
-      </c>
-      <c r="D240" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="n">
-        <v>240</v>
-      </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>http://static.buenosaires.gob.ar/gcaba_historico/banco-de-elementos-ortopedicos-beo</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>http://static.buenosaires.gob.ar/gcaba_historico/banco-de-elementos-ortopedicos-beo</t>
-        </is>
-      </c>
-      <c r="D241" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="n">
-        <v>241</v>
-      </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>https://www.buenosaires.gob.ar/copidis</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>https://www.buenosaires.gob.ar/copidis</t>
-        </is>
-      </c>
-      <c r="D242" s="4" t="inlineStr">
-        <is>
-          <t>❌ NO ENCONTRADA (404)</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="2" t="n">
-        <v>242</v>
-      </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rals.org.ar/</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>https://www.rals.org.ar/</t>
-        </is>
-      </c>
-      <c r="D243" s="3" t="inlineStr">
-        <is>
-          <t>✅ ONLINE (HTTP 200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="n">
-        <v>243</v>
-      </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/historias-compartidas</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/historias-compartidas</t>
-        </is>
-      </c>
-      <c r="D244" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="n">
-        <v>244</v>
-      </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/argentum-jazz-quinteto-0</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/argentum-jazz-quinteto-0</t>
-        </is>
-      </c>
-      <c r="D245" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="n">
-        <v>245</v>
-      </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/argentas-jazz</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/argentas-jazz</t>
-        </is>
-      </c>
-      <c r="D246" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="n">
-        <v>246</v>
-      </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/espacio-historico-de-la-pfa-ex-diario-critica</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/espacio-historico-de-la-pfa-ex-diario-critica</t>
-        </is>
-      </c>
-      <c r="D247" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="n">
-        <v>247</v>
-      </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/nina-suarez</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>https://buenosaires.gob.ar/descubrir/nina-suarez</t>
-        </is>
-      </c>
-      <c r="D248" s="4" t="inlineStr">
-        <is>
-          <t>❌ ERROR HTTP 500</t>
         </is>
       </c>
     </row>
